--- a/Task_06/DucNVFX14814_CN2_Review_Checklist.xlsx
+++ b/Task_06/DucNVFX14814_CN2_Review_Checklist.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Funix\4. CC4\5. LAB301x\LAB301x_01\Task_06\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE05F513-28F9-4E87-97CC-5C0CC0423F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,96 +36,92 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
-    <t xml:space="preserve">CHECKLIST TỰ KIỂM TRA - TASK 6: CN2 QUẢN LÝ VÉ DÒ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Học viên: DucNVFX14814 - Nguyễn Việt Đức</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hạng mục</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nội dung kiểm tra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã thực hiện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghi chú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CODE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã refactor mã nguồn theo đúng quy ước viết code đã thống nhất?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã loại bỏ các mã nguồn không sử dụng ra khỏi dự án chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã đặt tên và đặt lớp vào đúng nơi đã quy định (đã xác định ở bước 3) chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã thực hiện comment vào các đoạn code xử lý phức tạp chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã fix hết các lỗi đã tìm thấy chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã viết unit test cho các lớp DAO và BO chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã tạo các unit test và chạy cho các lớp DAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã kiểm tra mức độ bao phủ (coverage) của unit test trong dự án chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã tạo các unit test và chạy cho các lớp DAO, đầy đủ các method được dùng trong hệ thống</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã viết các tình huống cần kiểm tra cho các chức năng đã xây dựng chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã viết test case để kiểm tra các tình huống cần kiểm tra chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã hoàn thiện giao diện chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã chỉnh sửa cho nhất quán giữa các màn hình chưa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng số mục:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã thực hiện:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chưa thực hiện:</t>
+    <t>CHECKLIST TỰ KIỂM TRA - TASK 6: CN2 QUẢN LÝ VÉ DÒ</t>
+  </si>
+  <si>
+    <t>Học viên: DucNVFX14814 - Nguyễn Việt Đức</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Hạng mục</t>
+  </si>
+  <si>
+    <t>Nội dung kiểm tra</t>
+  </si>
+  <si>
+    <t>Đã thực hiện</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>CODE</t>
+  </si>
+  <si>
+    <t>Đã refactor mã nguồn theo đúng quy ước viết code đã thống nhất?</t>
+  </si>
+  <si>
+    <t>Đã loại bỏ các mã nguồn không sử dụng ra khỏi dự án chưa?</t>
+  </si>
+  <si>
+    <t>Đã đặt tên và đặt lớp vào đúng nơi đã quy định (đã xác định ở bước 3) chưa?</t>
+  </si>
+  <si>
+    <t>Đã thực hiện comment vào các đoạn code xử lý phức tạp chưa?</t>
+  </si>
+  <si>
+    <t>Đã fix hết các lỗi đã tìm thấy chưa?</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>Đã viết unit test cho các lớp DAO và BO chưa?</t>
+  </si>
+  <si>
+    <t>Đã kiểm tra mức độ bao phủ (coverage) của unit test trong dự án chưa?</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>Đã viết các tình huống cần kiểm tra cho các chức năng đã xây dựng chưa?</t>
+  </si>
+  <si>
+    <t>Đã viết test case để kiểm tra các tình huống cần kiểm tra chưa?</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Đã hoàn thiện giao diện chưa?</t>
+  </si>
+  <si>
+    <t>Đã chỉnh sửa cho nhất quán giữa các màn hình chưa?</t>
+  </si>
+  <si>
+    <t>Tổng số mục:</t>
+  </si>
+  <si>
+    <t>Đã thực hiện:</t>
+  </si>
+  <si>
+    <t>Chưa thực hiện:</t>
+  </si>
+  <si>
+    <t>Đã tạo các unit test và chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo các unit test và chạy cho các lớp DAO và BO, đầy đủ các method được dùng trong hệ thống</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,21 +130,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -142,7 +137,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Cambria"/>
       <family val="1"/>
@@ -156,14 +151,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
@@ -177,14 +172,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -212,14 +207,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FF999999"/>
       </left>
@@ -235,85 +230,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -372,47 +323,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -420,12 +387,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -454,7 +421,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -475,7 +442,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -526,7 +493,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -544,32 +511,34 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="45"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="8.67"/>
+    <col min="1" max="1" width="3.5546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="54" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="45" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,17 +548,17 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" s="3" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
@@ -606,8 +575,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -621,8 +590,8 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -636,8 +605,8 @@
       </c>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="n">
+    <row r="7" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
         <v>3</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -651,8 +620,8 @@
       </c>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="6">
         <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -666,8 +635,8 @@
       </c>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -681,8 +650,8 @@
       </c>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
         <v>6</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -695,110 +664,110 @@
         <v>5</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6">
         <v>7</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="E12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="E13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="6">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="E14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="6">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="n">
+      <c r="D17" s="10">
+        <f>COUNTA(E5:E15)</f>
         <v>11</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="8" t="s">
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="9" t="s">
+      <c r="D18" s="10">
+        <f>COUNTIF(E5:E15,"Đã thực hiện")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <f aca="false">COUNTA(E5:E15)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <f aca="false">COUNTIF(E5:E15,"Đã thực hiện")</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <f aca="false">COUNTIF(E5:E15,"Chưa thực hiện")</f>
+      <c r="D19" s="10">
+        <f>COUNTIF(E5:E15,"Chưa thực hiện")</f>
         <v>0</v>
       </c>
     </row>
@@ -808,17 +777,12 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E15" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="E5:E15" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Đã thực hiện,Chưa thực hiện"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>